--- a/data/trans_dic/DC-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/DC-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico</t>
+          <t>Población con dolor crónico (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,96; 30,44</t>
+          <t>24,94; 30,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,05; 20,28</t>
+          <t>15,24; 20,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,96; 18,2</t>
+          <t>13,07; 18,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,46; 38,14</t>
+          <t>30,81; 38,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,33; 37,16</t>
+          <t>31,82; 37,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,56; 33,79</t>
+          <t>28,71; 33,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,27; 29,14</t>
+          <t>23,57; 29,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>52,11; 57,85</t>
+          <t>51,98; 57,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,69; 33,46</t>
+          <t>29,79; 33,43</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,38; 27,16</t>
+          <t>23,71; 27,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,83; 23,85</t>
+          <t>19,46; 23,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,25; 48,85</t>
+          <t>44,22; 48,83</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,37; 14,6</t>
+          <t>11,36; 14,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 9,33</t>
+          <t>7,03; 9,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,5; 8,93</t>
+          <t>6,59; 8,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,97; 20,82</t>
+          <t>12,31; 20,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,96; 26,19</t>
+          <t>21,92; 26,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,64; 21,61</t>
+          <t>17,77; 21,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,18; 17,47</t>
+          <t>14,24; 17,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,91; 56,53</t>
+          <t>34,56; 58,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,02; 19,72</t>
+          <t>17,03; 19,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,44; 14,75</t>
+          <t>12,45; 14,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,66; 12,77</t>
+          <t>10,66; 12,72</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,83; 41,1</t>
+          <t>24,46; 39,64</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,89; 15,79</t>
+          <t>9,73; 15,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,3; 7,59</t>
+          <t>3,3; 7,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,88; 10,9</t>
+          <t>6,23; 11,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,64; 19,38</t>
+          <t>13,73; 19,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,19; 25,89</t>
+          <t>18,59; 26,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,91; 22,76</t>
+          <t>15,77; 22,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,48; 16,3</t>
+          <t>10,54; 16,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,15; 36,54</t>
+          <t>29,81; 36,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,7; 19,54</t>
+          <t>14,68; 19,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,81; 14,25</t>
+          <t>9,82; 14,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,95; 12,85</t>
+          <t>8,84; 12,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,64; 27,3</t>
+          <t>22,65; 27,23</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,32; 18,89</t>
+          <t>16,25; 18,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,38; 11,57</t>
+          <t>9,35; 11,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,51; 10,57</t>
+          <t>8,49; 10,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,59; 22,23</t>
+          <t>15,87; 22,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,44; 29,57</t>
+          <t>26,28; 29,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,55; 25,39</t>
+          <t>22,47; 25,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,04; 19,87</t>
+          <t>17,16; 19,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,59; 53,68</t>
+          <t>38,59; 53,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,7; 23,79</t>
+          <t>21,75; 23,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,35; 18,28</t>
+          <t>16,34; 18,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,16; 14,91</t>
+          <t>13,27; 14,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,32; 38,49</t>
+          <t>28,32; 38,24</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico</t>
+          <t>Población con dolor crónico (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>257500; 314015</t>
+          <t>257286; 317677</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>146670; 197673</t>
+          <t>148514; 197125</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97730; 137296</t>
+          <t>98608; 136332</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>156840; 196375</t>
+          <t>158642; 196704</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>425231; 488699</t>
+          <t>418478; 490055</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>382044; 452015</t>
+          <t>384061; 453143</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>231475; 289816</t>
+          <t>234410; 291952</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>393696; 437070</t>
+          <t>392712; 436027</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>696715; 785187</t>
+          <t>699059; 784546</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>540649; 628097</t>
+          <t>548299; 632773</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>346745; 417160</t>
+          <t>340413; 416171</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>562208; 620651</t>
+          <t>561766; 620374</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>192607; 247184</t>
+          <t>192403; 248110</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>131575; 183309</t>
+          <t>138072; 185520</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>134901; 185507</t>
+          <t>136800; 185333</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>297065; 476817</t>
+          <t>281903; 474851</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>348670; 415746</t>
+          <t>348064; 414692</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>310091; 379930</t>
+          <t>312390; 380702</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>281915; 347299</t>
+          <t>283090; 351006</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>758746; 1265089</t>
+          <t>773480; 1317387</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>558542; 646935</t>
+          <t>558702; 645191</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>463119; 549034</t>
+          <t>463501; 549365</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>433123; 519156</t>
+          <t>433248; 517156</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1124135; 1861038</t>
+          <t>1107557; 1794761</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>54540; 87059</t>
+          <t>53668; 87307</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15856; 36499</t>
+          <t>15856; 37951</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32179; 59631</t>
+          <t>34093; 62998</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>88175; 125304</t>
+          <t>88787; 127297</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>86641; 123339</t>
+          <t>88550; 125630</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68385; 104404</t>
+          <t>72325; 105220</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57563; 89499</t>
+          <t>57882; 91961</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>199104; 241324</t>
+          <t>196914; 240061</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>151113; 200872</t>
+          <t>150932; 200256</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>92170; 133880</t>
+          <t>92307; 134018</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>98068; 140885</t>
+          <t>96867; 139583</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>295943; 356770</t>
+          <t>296000; 355942</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>534641; 619071</t>
+          <t>532336; 618642</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>320740; 395538</t>
+          <t>319646; 393850</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>287371; 357037</t>
+          <t>286662; 354113</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>538023; 767500</t>
+          <t>547752; 760552</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>893553; 999137</t>
+          <t>887963; 995197</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>801468; 902297</t>
+          <t>798461; 903238</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>601748; 701767</t>
+          <t>606119; 700251</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1410141; 1961415</t>
+          <t>1409859; 1948328</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1444561; 1583231</t>
+          <t>1447744; 1578929</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1140098; 1274730</t>
+          <t>1139765; 1265201</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>909588; 1030247</t>
+          <t>916834; 1030627</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2012519; 2735244</t>
+          <t>2012031; 2716898</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/DC-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/DC-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>45,9%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,94; 30,79</t>
+          <t>24,91; 30,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,24; 20,23</t>
+          <t>15,11; 20,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,07; 18,07</t>
+          <t>13,19; 18,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,81; 38,2</t>
+          <t>29,17; 36,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,82; 37,26</t>
+          <t>31,88; 37,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,71; 33,87</t>
+          <t>28,6; 33,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,57; 29,35</t>
+          <t>23,5; 29,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51,98; 57,71</t>
+          <t>52,4; 57,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,79; 33,43</t>
+          <t>29,59; 33,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,71; 27,36</t>
+          <t>23,49; 27,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,46; 23,79</t>
+          <t>19,73; 23,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,22; 48,83</t>
+          <t>43,47; 48,08</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,36; 14,65</t>
+          <t>11,47; 14,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,03; 9,45</t>
+          <t>6,93; 9,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,59; 8,93</t>
+          <t>6,61; 9,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,31; 20,73</t>
+          <t>18,17; 21,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,92; 26,12</t>
+          <t>22,13; 26,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,77; 21,66</t>
+          <t>17,72; 21,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,24; 17,65</t>
+          <t>14,28; 17,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,56; 58,87</t>
+          <t>32,62; 36,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,03; 19,66</t>
+          <t>16,95; 19,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,45; 14,76</t>
+          <t>12,45; 14,82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,66; 12,72</t>
+          <t>10,68; 12,72</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,46; 39,64</t>
+          <t>25,75; 28,44</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,73; 15,83</t>
+          <t>9,71; 15,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,3; 7,89</t>
+          <t>3,32; 7,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,23; 11,52</t>
+          <t>6,03; 10,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,73; 19,69</t>
+          <t>13,67; 19,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,59; 26,37</t>
+          <t>18,94; 26,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,77; 22,94</t>
+          <t>15,41; 23,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,54; 16,75</t>
+          <t>10,14; 16,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,81; 36,35</t>
+          <t>30,61; 36,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,68; 19,48</t>
+          <t>14,73; 19,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,82; 14,26</t>
+          <t>10,0; 14,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,84; 12,74</t>
+          <t>8,95; 12,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,65; 27,23</t>
+          <t>22,94; 27,48</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,25; 18,88</t>
+          <t>16,27; 19,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,35; 11,52</t>
+          <t>9,41; 11,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,49; 10,48</t>
+          <t>8,59; 10,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,87; 22,03</t>
+          <t>19,92; 22,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,28; 29,45</t>
+          <t>26,41; 29,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,47; 25,41</t>
+          <t>22,43; 25,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,16; 19,83</t>
+          <t>17,06; 19,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,59; 53,32</t>
+          <t>37,4; 40,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,75; 23,72</t>
+          <t>21,63; 23,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,34; 18,14</t>
+          <t>16,26; 18,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,27; 14,92</t>
+          <t>13,18; 14,95</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,32; 38,24</t>
+          <t>29,36; 31,44</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>176964</t>
+          <t>190294</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>415336</t>
+          <t>452606</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>592300</t>
+          <t>642900</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>257286; 317677</t>
+          <t>256963; 312470</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>148514; 197125</t>
+          <t>147276; 195840</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98608; 136332</t>
+          <t>99498; 139589</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>158642; 196704</t>
+          <t>168765; 212348</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>418478; 490055</t>
+          <t>419236; 488136</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>384061; 453143</t>
+          <t>382609; 451647</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>234410; 291952</t>
+          <t>233713; 292686</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>392712; 436027</t>
+          <t>430711; 474493</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>699059; 784546</t>
+          <t>694397; 784843</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>548299; 632773</t>
+          <t>543204; 629194</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>340413; 416171</t>
+          <t>344995; 415116</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>561766; 620374</t>
+          <t>608789; 673340</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>411266</t>
+          <t>445924</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>934907</t>
+          <t>747582</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1346173</t>
+          <t>1193506</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>192403; 248110</t>
+          <t>194156; 250483</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>138072; 185520</t>
+          <t>136100; 184459</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>136800; 185333</t>
+          <t>137235; 187568</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>281903; 474851</t>
+          <t>405383; 487194</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>348064; 414692</t>
+          <t>351353; 413795</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>312390; 380702</t>
+          <t>311470; 381340</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>283090; 351006</t>
+          <t>284015; 351326</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>773480; 1317387</t>
+          <t>708307; 790733</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>558702; 645191</t>
+          <t>556191; 643576</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>463501; 549365</t>
+          <t>463447; 551381</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>433248; 517156</t>
+          <t>433959; 516869</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1107557; 1794761</t>
+          <t>1133299; 1251972</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>106456</t>
+          <t>116920</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>220119</t>
+          <t>246618</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>326575</t>
+          <t>363538</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>53668; 87307</t>
+          <t>53532; 85188</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15856; 37951</t>
+          <t>15956; 36656</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34093; 62998</t>
+          <t>32976; 59865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>88787; 127297</t>
+          <t>97271; 136812</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>88550; 125630</t>
+          <t>90243; 126358</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72325; 105220</t>
+          <t>70667; 106073</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57882; 91961</t>
+          <t>55706; 89732</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>196914; 240061</t>
+          <t>224945; 271492</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>150932; 200256</t>
+          <t>151425; 204707</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>92307; 134018</t>
+          <t>93949; 135278</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>96867; 139583</t>
+          <t>98108; 141045</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>296000; 355942</t>
+          <t>331760; 397448</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>694687</t>
+          <t>753138</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1570362</t>
+          <t>1446807</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2265049</t>
+          <t>2199945</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>532336; 618642</t>
+          <t>533223; 622922</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>319646; 393850</t>
+          <t>321907; 392794</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>286662; 354113</t>
+          <t>290103; 359156</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>547752; 760552</t>
+          <t>701398; 804928</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>887963; 995197</t>
+          <t>892353; 999527</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>798461; 903238</t>
+          <t>797330; 897768</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>606119; 700251</t>
+          <t>602624; 700339</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1409859; 1948328</t>
+          <t>1394365; 1499459</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1447744; 1578929</t>
+          <t>1439946; 1579800</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1139765; 1265201</t>
+          <t>1133885; 1261755</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>916834; 1030627</t>
+          <t>910583; 1033178</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2012031; 2716898</t>
+          <t>2128314; 2279187</t>
         </is>
       </c>
     </row>
